--- a/artfynd/A 63833-2025 artfynd.xlsx
+++ b/artfynd/A 63833-2025 artfynd.xlsx
@@ -963,10 +963,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131064790</v>
+        <v>131064794</v>
       </c>
       <c r="B5" t="n">
-        <v>80349</v>
+        <v>91829</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -974,23 +974,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -998,10 +994,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445585</v>
+        <v>445594</v>
       </c>
       <c r="R5" t="n">
-        <v>7037556</v>
+        <v>7037553</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,10 +1056,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131064794</v>
+        <v>131064790</v>
       </c>
       <c r="B6" t="n">
-        <v>91829</v>
+        <v>80349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1071,19 +1067,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445594</v>
+        <v>445585</v>
       </c>
       <c r="R6" t="n">
-        <v>7037553</v>
+        <v>7037556</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 63833-2025 artfynd.xlsx
+++ b/artfynd/A 63833-2025 artfynd.xlsx
@@ -963,10 +963,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131064794</v>
+        <v>131064790</v>
       </c>
       <c r="B5" t="n">
-        <v>91829</v>
+        <v>80349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -974,19 +974,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -994,10 +998,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445594</v>
+        <v>445585</v>
       </c>
       <c r="R5" t="n">
-        <v>7037553</v>
+        <v>7037556</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,10 +1060,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131064790</v>
+        <v>131064794</v>
       </c>
       <c r="B6" t="n">
-        <v>80349</v>
+        <v>91829</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1067,23 +1071,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445585</v>
+        <v>445594</v>
       </c>
       <c r="R6" t="n">
-        <v>7037556</v>
+        <v>7037553</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 63833-2025 artfynd.xlsx
+++ b/artfynd/A 63833-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131064792</v>
       </c>
       <c r="B2" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -768,10 +768,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131064793</v>
+        <v>131064788</v>
       </c>
       <c r="B3" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -779,19 +779,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -799,10 +803,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445757</v>
+        <v>445736</v>
       </c>
       <c r="R3" t="n">
-        <v>7037091</v>
+        <v>7037107</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -835,6 +839,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -861,10 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131064788</v>
+        <v>131064793</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>91830</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -872,23 +881,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -896,10 +901,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445736</v>
+        <v>445757</v>
       </c>
       <c r="R4" t="n">
-        <v>7037107</v>
+        <v>7037091</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -932,11 +937,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,7 +966,7 @@
         <v>131064790</v>
       </c>
       <c r="B5" t="n">
-        <v>80349</v>
+        <v>80350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         <v>131064794</v>
       </c>
       <c r="B6" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 63833-2025 artfynd.xlsx
+++ b/artfynd/A 63833-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131064792</v>
       </c>
       <c r="B2" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -768,10 +768,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131064788</v>
+        <v>131064793</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>91833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -779,23 +779,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -803,10 +799,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445736</v>
+        <v>445757</v>
       </c>
       <c r="R3" t="n">
-        <v>7037107</v>
+        <v>7037091</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -839,11 +835,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,10 +861,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131064793</v>
+        <v>131064788</v>
       </c>
       <c r="B4" t="n">
-        <v>91830</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,19 +872,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -901,10 +896,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445757</v>
+        <v>445736</v>
       </c>
       <c r="R4" t="n">
-        <v>7037091</v>
+        <v>7037107</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -937,6 +932,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1063,7 +1063,7 @@
         <v>131064794</v>
       </c>
       <c r="B6" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 63833-2025 artfynd.xlsx
+++ b/artfynd/A 63833-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131064792</v>
       </c>
       <c r="B2" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -768,10 +768,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131064793</v>
+        <v>131064788</v>
       </c>
       <c r="B3" t="n">
-        <v>91833</v>
+        <v>57884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -779,19 +779,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -799,10 +803,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445757</v>
+        <v>445736</v>
       </c>
       <c r="R3" t="n">
-        <v>7037091</v>
+        <v>7037107</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -835,6 +839,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -861,10 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131064788</v>
+        <v>131064793</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>91834</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -872,23 +881,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -896,10 +901,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445736</v>
+        <v>445757</v>
       </c>
       <c r="R4" t="n">
-        <v>7037107</v>
+        <v>7037091</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -932,11 +937,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,7 +966,7 @@
         <v>131064790</v>
       </c>
       <c r="B5" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         <v>131064794</v>
       </c>
       <c r="B6" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 63833-2025 artfynd.xlsx
+++ b/artfynd/A 63833-2025 artfynd.xlsx
@@ -768,10 +768,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131064788</v>
+        <v>131064793</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>91834</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -779,23 +779,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -803,10 +799,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445736</v>
+        <v>445757</v>
       </c>
       <c r="R3" t="n">
-        <v>7037107</v>
+        <v>7037091</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -839,11 +835,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,10 +861,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131064793</v>
+        <v>131064788</v>
       </c>
       <c r="B4" t="n">
-        <v>91834</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,19 +872,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -901,10 +896,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445757</v>
+        <v>445736</v>
       </c>
       <c r="R4" t="n">
-        <v>7037091</v>
+        <v>7037107</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -937,6 +932,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 63833-2025 artfynd.xlsx
+++ b/artfynd/A 63833-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131064792</v>
       </c>
       <c r="B2" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -768,10 +768,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131064793</v>
+        <v>131064788</v>
       </c>
       <c r="B3" t="n">
-        <v>91834</v>
+        <v>57886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -779,19 +779,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -799,10 +803,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445757</v>
+        <v>445736</v>
       </c>
       <c r="R3" t="n">
-        <v>7037091</v>
+        <v>7037107</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -835,6 +839,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -861,10 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131064788</v>
+        <v>131064793</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>91836</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -872,23 +881,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -896,10 +901,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445736</v>
+        <v>445757</v>
       </c>
       <c r="R4" t="n">
-        <v>7037107</v>
+        <v>7037091</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -932,11 +937,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,7 +966,7 @@
         <v>131064790</v>
       </c>
       <c r="B5" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         <v>131064794</v>
       </c>
       <c r="B6" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>131064789</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>131064787</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 63833-2025 artfynd.xlsx
+++ b/artfynd/A 63833-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131064792</v>
       </c>
       <c r="B2" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -768,10 +768,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131064788</v>
+        <v>131064793</v>
       </c>
       <c r="B3" t="n">
-        <v>57886</v>
+        <v>91837</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -779,23 +779,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -803,10 +799,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445736</v>
+        <v>445757</v>
       </c>
       <c r="R3" t="n">
-        <v>7037107</v>
+        <v>7037091</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -839,11 +835,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,10 +861,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131064793</v>
+        <v>131064788</v>
       </c>
       <c r="B4" t="n">
-        <v>91836</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,19 +872,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -901,10 +896,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445757</v>
+        <v>445736</v>
       </c>
       <c r="R4" t="n">
-        <v>7037091</v>
+        <v>7037107</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -937,6 +932,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -963,10 +963,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131064790</v>
+        <v>131064794</v>
       </c>
       <c r="B5" t="n">
-        <v>80353</v>
+        <v>91837</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -974,23 +974,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -998,10 +994,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445585</v>
+        <v>445594</v>
       </c>
       <c r="R5" t="n">
-        <v>7037556</v>
+        <v>7037553</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,10 +1056,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131064794</v>
+        <v>131064790</v>
       </c>
       <c r="B6" t="n">
-        <v>91836</v>
+        <v>80354</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1071,19 +1067,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445594</v>
+        <v>445585</v>
       </c>
       <c r="R6" t="n">
-        <v>7037553</v>
+        <v>7037556</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1156,7 +1156,7 @@
         <v>131064789</v>
       </c>
       <c r="B7" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>131064787</v>
       </c>
       <c r="B8" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 63833-2025 artfynd.xlsx
+++ b/artfynd/A 63833-2025 artfynd.xlsx
@@ -768,10 +768,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131064793</v>
+        <v>131064788</v>
       </c>
       <c r="B3" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -779,19 +779,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -799,10 +803,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445757</v>
+        <v>445736</v>
       </c>
       <c r="R3" t="n">
-        <v>7037091</v>
+        <v>7037107</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -835,6 +839,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -861,10 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131064788</v>
+        <v>131064793</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>91837</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -872,23 +881,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -896,10 +901,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445736</v>
+        <v>445757</v>
       </c>
       <c r="R4" t="n">
-        <v>7037107</v>
+        <v>7037091</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -932,11 +937,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -963,10 +963,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131064794</v>
+        <v>131064790</v>
       </c>
       <c r="B5" t="n">
-        <v>91837</v>
+        <v>80354</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -974,19 +974,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -994,10 +998,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445594</v>
+        <v>445585</v>
       </c>
       <c r="R5" t="n">
-        <v>7037553</v>
+        <v>7037556</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,10 +1060,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131064790</v>
+        <v>131064794</v>
       </c>
       <c r="B6" t="n">
-        <v>80354</v>
+        <v>91837</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1067,23 +1071,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445585</v>
+        <v>445594</v>
       </c>
       <c r="R6" t="n">
-        <v>7037556</v>
+        <v>7037553</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 63833-2025 artfynd.xlsx
+++ b/artfynd/A 63833-2025 artfynd.xlsx
@@ -768,10 +768,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131064788</v>
+        <v>131064793</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>91837</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -779,23 +779,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -803,10 +799,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445736</v>
+        <v>445757</v>
       </c>
       <c r="R3" t="n">
-        <v>7037107</v>
+        <v>7037091</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -839,11 +835,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,10 +861,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131064793</v>
+        <v>131064788</v>
       </c>
       <c r="B4" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,19 +872,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -901,10 +896,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445757</v>
+        <v>445736</v>
       </c>
       <c r="R4" t="n">
-        <v>7037091</v>
+        <v>7037107</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -937,6 +932,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -963,10 +963,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131064790</v>
+        <v>131064794</v>
       </c>
       <c r="B5" t="n">
-        <v>80354</v>
+        <v>91837</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -974,23 +974,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -998,10 +994,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445585</v>
+        <v>445594</v>
       </c>
       <c r="R5" t="n">
-        <v>7037556</v>
+        <v>7037553</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,10 +1056,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131064794</v>
+        <v>131064790</v>
       </c>
       <c r="B6" t="n">
-        <v>91837</v>
+        <v>80354</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1071,19 +1067,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445594</v>
+        <v>445585</v>
       </c>
       <c r="R6" t="n">
-        <v>7037553</v>
+        <v>7037556</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 63833-2025 artfynd.xlsx
+++ b/artfynd/A 63833-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131064792</v>
       </c>
       <c r="B2" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>131064793</v>
       </c>
       <c r="B3" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>131064788</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -963,10 +963,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131064794</v>
+        <v>131064790</v>
       </c>
       <c r="B5" t="n">
-        <v>91837</v>
+        <v>80355</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -974,19 +974,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -994,10 +998,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445594</v>
+        <v>445585</v>
       </c>
       <c r="R5" t="n">
-        <v>7037553</v>
+        <v>7037556</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,10 +1060,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131064790</v>
+        <v>131064794</v>
       </c>
       <c r="B6" t="n">
-        <v>80354</v>
+        <v>91838</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1067,23 +1071,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445585</v>
+        <v>445594</v>
       </c>
       <c r="R6" t="n">
-        <v>7037556</v>
+        <v>7037553</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1156,7 +1156,7 @@
         <v>131064789</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>131064787</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 63833-2025 artfynd.xlsx
+++ b/artfynd/A 63833-2025 artfynd.xlsx
@@ -1156,7 +1156,7 @@
         <v>131064789</v>
       </c>
       <c r="B7" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>131064787</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 63833-2025 artfynd.xlsx
+++ b/artfynd/A 63833-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131064792</v>
+        <v>131064791</v>
       </c>
       <c r="B2" t="n">
-        <v>91838</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445658</v>
+        <v>445724</v>
       </c>
       <c r="R2" t="n">
-        <v>7037400</v>
+        <v>7037231</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -768,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131064793</v>
+        <v>131064790</v>
       </c>
       <c r="B3" t="n">
-        <v>91838</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -779,19 +783,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -799,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445757</v>
+        <v>445585</v>
       </c>
       <c r="R3" t="n">
-        <v>7037091</v>
+        <v>7037556</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131064788</v>
+        <v>131064787</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,16 +898,24 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Svedjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445736</v>
+        <v>445713</v>
       </c>
       <c r="R4" t="n">
-        <v>7037107</v>
+        <v>7037170</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -936,14 +952,14 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål? Ca 4,5m upp i grantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -963,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131064790</v>
+        <v>131064788</v>
       </c>
       <c r="B5" t="n">
-        <v>80355</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -974,21 +990,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -998,10 +1014,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445585</v>
+        <v>445736</v>
       </c>
       <c r="R5" t="n">
-        <v>7037556</v>
+        <v>7037107</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1034,6 +1050,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1060,10 +1081,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131064794</v>
+        <v>131064789</v>
       </c>
       <c r="B6" t="n">
-        <v>91838</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1071,30 +1092,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svedjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445594</v>
+        <v>445611</v>
       </c>
       <c r="R6" t="n">
-        <v>7037553</v>
+        <v>7037776</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,64 +1194,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131064789</v>
+        <v>91489127</v>
       </c>
       <c r="B7" t="n">
-        <v>57891</v>
+        <v>98137</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>222741</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svedjebodarna, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445611</v>
+        <v>445686</v>
       </c>
       <c r="R7" t="n">
-        <v>7037776</v>
+        <v>7037143</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1234,12 +1259,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1254,68 +1279,64 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131064787</v>
+        <v>91489129</v>
       </c>
       <c r="B8" t="n">
-        <v>57891</v>
+        <v>98137</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>222741</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svedjebodarna, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445713</v>
+        <v>445525</v>
       </c>
       <c r="R8" t="n">
-        <v>7037170</v>
+        <v>7037654</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1339,24 +1360,19 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Bohål? Ca 4,5m upp i grantickerötad granhögstubbe</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="b">
         <v>0</v>
@@ -1364,15 +1380,125 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>91489132</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98137</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222741</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Finbräken</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cystopteris montana</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>445594</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7037692</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2018-07-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2018-10-31</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Vid bäck</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63833-2025 artfynd.xlsx
+++ b/artfynd/A 63833-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064791</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064787</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064788</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91489127</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064790</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1292,6 +1322,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064789</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1393,6 +1428,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91489129</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1499,8 +1539,23 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91489132</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 63833-2025 artfynd.xlsx
+++ b/artfynd/A 63833-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,53 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131064787</v>
+        <v>135917704</v>
       </c>
       <c r="B3" t="n">
-        <v>57953</v>
+        <v>79441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svedjebodarna, Jmt</t>
+          <t>Svedbodarna sv, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445713</v>
+        <v>445714</v>
       </c>
       <c r="R3" t="n">
-        <v>7037170</v>
+        <v>7037317</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,24 +847,29 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bohål? Ca 4,5m upp i grantickerötad granhögstubbe</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -891,13 +888,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131064787</t>
+          <t>https://artportalen.se/Sighting/135917704</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131064788</v>
+        <v>131064787</v>
       </c>
       <c r="B4" t="n">
         <v>57953</v>
@@ -926,16 +923,24 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Svedjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445736</v>
+        <v>445713</v>
       </c>
       <c r="R4" t="n">
-        <v>7037107</v>
+        <v>7037170</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,14 +977,14 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål? Ca 4,5m upp i grantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -998,54 +1003,54 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131064788</t>
+          <t>https://artportalen.se/Sighting/131064787</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91489127</v>
+        <v>131064788</v>
       </c>
       <c r="B5" t="n">
-        <v>98137</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222741</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jämtland, Jmt</t>
+          <t>Svedjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445686</v>
+        <v>445736</v>
       </c>
       <c r="R5" t="n">
-        <v>7037143</v>
+        <v>7037107</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1069,12 +1074,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,69 +1099,65 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91489127</t>
+          <t>https://artportalen.se/Sighting/131064788</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131064790</v>
+        <v>91489127</v>
       </c>
       <c r="B6" t="n">
-        <v>80432</v>
+        <v>98137</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>222741</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svedjebodarna, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445585</v>
+        <v>445686</v>
       </c>
       <c r="R6" t="n">
-        <v>7037556</v>
+        <v>7037143</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1175,12 +1181,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,27 +1201,31 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131064790</t>
+          <t>https://artportalen.se/Sighting/91489127</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131064789</v>
+        <v>131064790</v>
       </c>
       <c r="B7" t="n">
-        <v>57953</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1223,50 +1233,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svedjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445611</v>
+        <v>445585</v>
       </c>
       <c r="R7" t="n">
-        <v>7037776</v>
+        <v>7037556</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,54 +1318,70 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131064789</t>
+          <t>https://artportalen.se/Sighting/131064790</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>91489129</v>
+        <v>131064789</v>
       </c>
       <c r="B8" t="n">
-        <v>98137</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222741</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Jämtland, Jmt</t>
+          <t>Svedjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445525</v>
+        <v>445611</v>
       </c>
       <c r="R8" t="n">
-        <v>7037654</v>
+        <v>7037776</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1395,12 +1405,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1415,28 +1425,24 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91489129</t>
+          <t>https://artportalen.se/Sighting/131064789</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>91489132</v>
+        <v>91489129</v>
       </c>
       <c r="B9" t="n">
         <v>98137</v>
@@ -1471,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445594</v>
+        <v>445525</v>
       </c>
       <c r="R9" t="n">
-        <v>7037692</v>
+        <v>7037654</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1518,11 +1524,6 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Vid bäck</t>
-        </is>
-      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
@@ -1540,6 +1541,117 @@
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91489129</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>91489132</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98137</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222741</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Finbräken</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cystopteris montana</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>445594</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7037692</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2018-07-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2018-10-31</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Vid bäck</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/91489132</t>
         </is>
@@ -1555,6 +1667,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63833-2025 artfynd.xlsx
+++ b/artfynd/A 63833-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135917704</v>
       </c>
       <c r="B3" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63833-2025 artfynd.xlsx
+++ b/artfynd/A 63833-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135917704</v>
       </c>
       <c r="B3" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63833-2025 artfynd.xlsx
+++ b/artfynd/A 63833-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135917704</v>
       </c>
       <c r="B3" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63833-2025 artfynd.xlsx
+++ b/artfynd/A 63833-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135917704</v>
       </c>
       <c r="B3" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63833-2025 artfynd.xlsx
+++ b/artfynd/A 63833-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135917704</v>
       </c>
       <c r="B3" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63833-2025 artfynd.xlsx
+++ b/artfynd/A 63833-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135917704</v>
       </c>
       <c r="B3" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63833-2025 artfynd.xlsx
+++ b/artfynd/A 63833-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135917704</v>
       </c>
       <c r="B3" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63833-2025 artfynd.xlsx
+++ b/artfynd/A 63833-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135917704</v>
       </c>
       <c r="B3" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63833-2025 artfynd.xlsx
+++ b/artfynd/A 63833-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135917704</v>
       </c>
       <c r="B3" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
